--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>100.6146792855601</v>
+        <v>16.34988538390352</v>
       </c>
       <c r="D2" t="n">
-        <v>87.53484693300945</v>
+        <v>14.22441262661404</v>
       </c>
       <c r="E2" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F2" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.06533692224919</v>
+        <v>12.36061724986549</v>
       </c>
       <c r="D3" t="n">
-        <v>74.51074927397801</v>
+        <v>12.10799675702143</v>
       </c>
       <c r="E3" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F3" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.30598154777834</v>
+        <v>13.04972200151398</v>
       </c>
       <c r="D4" t="n">
-        <v>73.92656810413511</v>
+        <v>12.01306731692196</v>
       </c>
       <c r="E4" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F4" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.24928866777609</v>
+        <v>9.140509408513616</v>
       </c>
       <c r="D5" t="n">
-        <v>55.70468482173311</v>
+        <v>9.05201128353163</v>
       </c>
       <c r="E5" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F5" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.88664305681535</v>
+        <v>9.731579496732495</v>
       </c>
       <c r="D6" t="n">
-        <v>58.24910944311048</v>
+        <v>9.465480284505453</v>
       </c>
       <c r="E6" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F6" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.26774862533842</v>
+        <v>5.568509151617493</v>
       </c>
       <c r="D7" t="n">
-        <v>33.74539387914031</v>
+        <v>5.4836265053603</v>
       </c>
       <c r="E7" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F7" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.63385762939978</v>
+        <v>5.953001864777464</v>
       </c>
       <c r="D8" t="n">
-        <v>35.14722723180726</v>
+        <v>5.711424425168681</v>
       </c>
       <c r="E8" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F8" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>69.70210434375525</v>
+        <v>11.32659195586023</v>
       </c>
       <c r="D9" t="n">
-        <v>44.61229112334825</v>
+        <v>7.24949730754409</v>
       </c>
       <c r="E9" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F9" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>71.98332354839853</v>
+        <v>11.69729007661476</v>
       </c>
       <c r="D10" t="n">
-        <v>42.69319501075972</v>
+        <v>6.937644189248454</v>
       </c>
       <c r="E10" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F10" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.48060018221749</v>
+        <v>7.715597529610342</v>
       </c>
       <c r="D11" t="n">
-        <v>15.70031846810758</v>
+        <v>2.551301751067482</v>
       </c>
       <c r="E11" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F11" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>49.99174176802323</v>
+        <v>8.123658037303775</v>
       </c>
       <c r="D12" t="n">
-        <v>24.35514560182573</v>
+        <v>3.957711160296681</v>
       </c>
       <c r="E12" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F12" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>48.80649160892215</v>
+        <v>7.93105488644985</v>
       </c>
       <c r="D13" t="n">
-        <v>12.74754878398196</v>
+        <v>2.071476677397069</v>
       </c>
       <c r="E13" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F13" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>60.07217803602146</v>
+        <v>9.761728930853488</v>
       </c>
       <c r="D14" t="n">
-        <v>37.04719442160867</v>
+        <v>6.020169093511408</v>
       </c>
       <c r="E14" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F14" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>88.26887686279684</v>
+        <v>14.34369249020449</v>
       </c>
       <c r="D15" t="n">
-        <v>62.78382306474058</v>
+        <v>10.20237124802035</v>
       </c>
       <c r="E15" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F15" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>73.77162035054246</v>
+        <v>11.98788830696315</v>
       </c>
       <c r="D16" t="n">
-        <v>53.93381292205946</v>
+        <v>8.764244599834662</v>
       </c>
       <c r="E16" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F16" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>97.3021686998876</v>
+        <v>15.81160241373174</v>
       </c>
       <c r="D17" t="n">
-        <v>70.94016293457406</v>
+        <v>11.52777647686828</v>
       </c>
       <c r="E17" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F17" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>88.45691799749557</v>
+        <v>14.37424917459303</v>
       </c>
       <c r="D18" t="n">
-        <v>67.07483580833392</v>
+        <v>10.89966081885426</v>
       </c>
       <c r="E18" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F18" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>101.8830314619688</v>
+        <v>16.55599261256994</v>
       </c>
       <c r="D19" t="n">
-        <v>77.69329051721134</v>
+        <v>12.62515970904684</v>
       </c>
       <c r="E19" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F19" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>83.21564617050122</v>
+        <v>13.52254250270645</v>
       </c>
       <c r="D20" t="n">
-        <v>63.4945457380674</v>
+        <v>10.31786368243595</v>
       </c>
       <c r="E20" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F20" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>87.05152765800349</v>
+        <v>14.14587324442557</v>
       </c>
       <c r="D21" t="n">
-        <v>17.50110845236736</v>
+        <v>2.843930123509697</v>
       </c>
       <c r="E21" t="n">
-        <v>20.16145464705781</v>
+        <v>3.276236380146894</v>
       </c>
       <c r="F21" t="n">
-        <v>21.85099627270682</v>
+        <v>3.550786894314858</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
